--- a/tests/fixtures/lom/P904225-1-LOM.xlsx
+++ b/tests/fixtures/lom/P904225-1-LOM.xlsx
@@ -14,35 +14,20 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>P904225-1</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>ITEM</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>PART NO</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ITEM</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>PART NO</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
@@ -51,407 +36,286 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1002076-1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>904225-1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>PLATE A</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1002038-1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>904225-2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>PLATE B</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1002071-1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>904225-3</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>PLATE C</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11694-1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>904225-4</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>PLATE D</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1002068-1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>904225-5</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>PLATE E</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1002069-1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>904225-6</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>PLATE F</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>P904245-1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>904225-7</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>PLATE G</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1002067-1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>904225-8</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>PLATE H</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>P904231-1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>904225-9</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>PLATE J</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>P904230-1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>904225-10</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>PLATE K</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>P904226-1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PLATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>89176-1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>WELDING WIRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>P904225-1</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>WELDMENT PLATE</t>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>WELDMENT</t>
         </is>
       </c>
     </row>
@@ -487,220 +351,220 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>904225-1</t>
+          <t>1002076-1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PLATE A</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>904225-2</t>
+          <t>1002038-1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PLATE B</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>904225-3</t>
+          <t>1002071-1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PLATE C</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>904225-4</t>
+          <t>11694-1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PLATE D</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>904225-5</t>
+          <t>1002068-1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PLATE E</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>904225-6</t>
+          <t>1002069-1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PLATE F</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>904225-7</t>
+          <t>P904245-1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PLATE G</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>904225-8</t>
+          <t>1002067-1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PLATE H</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>904225-9</t>
+          <t>P904231-1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PLATE J</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>904225-10</t>
+          <t>P904230-1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PLATE K</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
@@ -712,17 +576,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>P904226-1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PLATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>P904225-1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>WELDMENT PLATE</t>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>WELDMENT</t>
         </is>
       </c>
     </row>
